--- a/S15/T174/S15_T174_decision_6.xlsx
+++ b/S15/T174/S15_T174_decision_6.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="72">
   <si>
     <t xml:space="preserve">c1</t>
   </si>
@@ -139,73 +139,73 @@
     <t xml:space="preserve">x 1 batch</t>
   </si>
   <si>
+    <t xml:space="preserve">Puree Purchasing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x 1 bin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concentrate Purchasing for Arnhem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kemijarvi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rauma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cordial packaging</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x 20 pallets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bucharest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cordial production</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Madrid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bottle Purchasing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sugar Purchasing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x 1 tonne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concentrate Purchasing for Vesoul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCFFCC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intercontinental transport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puree transport to Arnhem</t>
+  </si>
+  <si>
     <t xml:space="preserve">Berlin</t>
   </si>
   <si>
-    <t xml:space="preserve">Puree Purchasing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x 1 bin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rauma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concentrate Purchasing for Arnhem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kemijarvi</t>
+    <t xml:space="preserve">Concentrate transport to Arnhem</t>
   </si>
   <si>
     <t xml:space="preserve">Warsaw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cordial packaging</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x 20 pallets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bucharest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cordial production</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bottle Purchasing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sugar Purchasing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x 1 tonne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concentrate Purchasing for Vesoul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCFFCC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intercontinental transport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puree transport to Arnhem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Madrid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concentrate transport to Arnhem</t>
   </si>
   <si>
     <t xml:space="preserve">Concentrate transport to Vesoul</t>
@@ -1592,7 +1592,7 @@
         <v>26</v>
       </c>
       <c r="K11" s="28" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L11" s="29" t="s">
         <v>27</v>
@@ -1609,7 +1609,9 @@
         <v>29</v>
       </c>
       <c r="D12" s="30"/>
-      <c r="E12" s="31"/>
+      <c r="E12" s="31" t="n">
+        <v>13</v>
+      </c>
       <c r="F12" s="31"/>
       <c r="G12" s="32"/>
       <c r="H12" s="26" t="str">
@@ -1623,7 +1625,7 @@
         <v>30</v>
       </c>
       <c r="K12" s="34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L12" s="35" t="s">
         <v>31</v>
@@ -1653,9 +1655,7 @@
       <c r="J13" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="K13" s="34" t="n">
-        <v>0</v>
-      </c>
+      <c r="K13" s="34"/>
       <c r="L13" s="35" t="s">
         <v>35</v>
       </c>
@@ -1680,9 +1680,7 @@
       <c r="J14" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="K14" s="34" t="n">
-        <v>0</v>
-      </c>
+      <c r="K14" s="34"/>
       <c r="L14" s="35" t="s">
         <v>35</v>
       </c>
@@ -1695,14 +1693,14 @@
         <v>28</v>
       </c>
       <c r="C15" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="31" t="n">
-        <v>55</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="D15" s="31"/>
       <c r="E15" s="31"/>
       <c r="F15" s="31"/>
-      <c r="G15" s="32"/>
+      <c r="G15" s="32" t="n">
+        <v>13</v>
+      </c>
       <c r="H15" s="26" t="str">
         <f aca="false">IF(AND(B15="",OR(C15&lt;&gt;"",D15&lt;&gt;"",E15&lt;&gt;"",F15&lt;&gt;"",G15&lt;&gt;"")),"A lorry must be selected",IF(AND(C15="",OR(D15&lt;&gt;"",E15&lt;&gt;"",F15&lt;&gt;"",G15&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -1714,7 +1712,7 @@
         <v>37</v>
       </c>
       <c r="K15" s="34" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L15" s="35" t="s">
         <v>38</v>
@@ -1728,13 +1726,13 @@
         <v>28</v>
       </c>
       <c r="C16" s="41" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="31"/>
+        <v>22</v>
+      </c>
+      <c r="D16" s="31" t="n">
+        <v>66</v>
+      </c>
       <c r="E16" s="31"/>
-      <c r="F16" s="31" t="n">
-        <v>23</v>
-      </c>
+      <c r="F16" s="31"/>
       <c r="G16" s="32"/>
       <c r="H16" s="26" t="str">
         <f aca="false">IF(AND(B16="",OR(C16&lt;&gt;"",D16&lt;&gt;"",E16&lt;&gt;"",F16&lt;&gt;"",G16&lt;&gt;"")),"A lorry must be selected",IF(AND(C16="",OR(D16&lt;&gt;"",E16&lt;&gt;"",F16&lt;&gt;"",G16&lt;&gt;"")),"A town must be selected",""))</f>
@@ -1744,30 +1742,22 @@
         <v>6</v>
       </c>
       <c r="J16" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="K16" s="34"/>
+      <c r="L16" s="35" t="s">
         <v>40</v>
-      </c>
-      <c r="K16" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="35" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B17" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="41" t="s">
-        <v>42</v>
-      </c>
+      <c r="B17" s="40"/>
+      <c r="C17" s="41"/>
       <c r="D17" s="31"/>
       <c r="E17" s="31"/>
-      <c r="F17" s="31" t="n">
-        <v>14</v>
-      </c>
+      <c r="F17" s="31"/>
       <c r="G17" s="32"/>
       <c r="H17" s="26" t="str">
         <f aca="false">IF(AND(B17="",OR(C17&lt;&gt;"",D17&lt;&gt;"",E17&lt;&gt;"",F17&lt;&gt;"",G17&lt;&gt;"")),"A lorry must be selected",IF(AND(C17="",OR(D17&lt;&gt;"",E17&lt;&gt;"",F17&lt;&gt;"",G17&lt;&gt;"")),"A town must be selected",""))</f>
@@ -1777,13 +1767,11 @@
         <v>7</v>
       </c>
       <c r="J17" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="K17" s="43" t="n">
-        <v>0</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="K17" s="43"/>
       <c r="L17" s="44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1794,12 +1782,12 @@
         <v>28</v>
       </c>
       <c r="C18" s="41" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D18" s="31"/>
       <c r="E18" s="31"/>
       <c r="F18" s="31" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="G18" s="32"/>
       <c r="H18" s="26" t="str">
@@ -1815,13 +1803,13 @@
         <v>28</v>
       </c>
       <c r="C19" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="31" t="n">
-        <v>66</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="D19" s="31"/>
       <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
+      <c r="F19" s="31" t="n">
+        <v>33</v>
+      </c>
       <c r="G19" s="32"/>
       <c r="H19" s="26" t="str">
         <f aca="false">IF(AND(B19="",OR(C19&lt;&gt;"",D19&lt;&gt;"",E19&lt;&gt;"",F19&lt;&gt;"",G19&lt;&gt;"")),"A lorry must be selected",IF(AND(C19="",OR(D19&lt;&gt;"",E19&lt;&gt;"",F19&lt;&gt;"",G19&lt;&gt;"")),"A town must be selected",""))</f>
@@ -1839,13 +1827,13 @@
         <v>28</v>
       </c>
       <c r="C20" s="41" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20" s="31"/>
+        <v>22</v>
+      </c>
+      <c r="D20" s="31" t="n">
+        <v>66</v>
+      </c>
       <c r="E20" s="31"/>
-      <c r="F20" s="31" t="n">
-        <v>22</v>
-      </c>
+      <c r="F20" s="31"/>
       <c r="G20" s="32"/>
       <c r="H20" s="26" t="str">
         <f aca="false">IF(AND(B20="",OR(C20&lt;&gt;"",D20&lt;&gt;"",E20&lt;&gt;"",F20&lt;&gt;"",G20&lt;&gt;"")),"A lorry must be selected",IF(AND(C20="",OR(D20&lt;&gt;"",E20&lt;&gt;"",F20&lt;&gt;"",G20&lt;&gt;"")),"A town must be selected",""))</f>
@@ -1860,12 +1848,12 @@
         <v>28</v>
       </c>
       <c r="C21" s="41" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D21" s="31"/>
       <c r="E21" s="31"/>
       <c r="F21" s="31" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G21" s="32"/>
       <c r="H21" s="26" t="str">
@@ -1876,13 +1864,13 @@
         <v>1</v>
       </c>
       <c r="J21" s="45" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K21" s="28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L21" s="45" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1893,12 +1881,12 @@
         <v>28</v>
       </c>
       <c r="C22" s="41" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D22" s="31"/>
       <c r="E22" s="31"/>
       <c r="F22" s="31" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G22" s="32"/>
       <c r="H22" s="26" t="str">
@@ -1909,11 +1897,9 @@
         <v>2</v>
       </c>
       <c r="J22" s="46" t="s">
-        <v>50</v>
-      </c>
-      <c r="K22" s="34" t="n">
-        <v>0</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="K22" s="34"/>
       <c r="L22" s="46" t="s">
         <v>31</v>
       </c>
@@ -1923,13 +1909,13 @@
         <v>13</v>
       </c>
       <c r="B23" s="40" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C23" s="41" t="s">
         <v>22</v>
       </c>
       <c r="D23" s="31" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E23" s="31"/>
       <c r="F23" s="31"/>
@@ -1966,15 +1952,15 @@
         <v>14</v>
       </c>
       <c r="B24" s="40" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C24" s="41" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D24" s="31"/>
       <c r="E24" s="31"/>
       <c r="F24" s="31" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G24" s="32"/>
       <c r="H24" s="26" t="str">
@@ -1987,7 +1973,9 @@
       <c r="J24" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="K24" s="34"/>
+      <c r="K24" s="34" t="n">
+        <v>1</v>
+      </c>
       <c r="L24" s="46" t="s">
         <v>35</v>
       </c>
@@ -1997,16 +1985,16 @@
         <v>15</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C25" s="41" t="s">
-        <v>52</v>
-      </c>
-      <c r="D25" s="31"/>
+        <v>22</v>
+      </c>
+      <c r="D25" s="31" t="n">
+        <v>24</v>
+      </c>
       <c r="E25" s="31"/>
-      <c r="F25" s="31" t="n">
-        <v>20</v>
-      </c>
+      <c r="F25" s="31"/>
       <c r="G25" s="32"/>
       <c r="H25" s="26" t="str">
         <f aca="false">IF(AND(B25="",OR(C25&lt;&gt;"",D25&lt;&gt;"",E25&lt;&gt;"",F25&lt;&gt;"",G25&lt;&gt;"")),"A lorry must be selected",IF(AND(C25="",OR(D25&lt;&gt;"",E25&lt;&gt;"",F25&lt;&gt;"",G25&lt;&gt;"")),"A town must be selected",""))</f>
@@ -2016,11 +2004,9 @@
         <v>5</v>
       </c>
       <c r="J25" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="K25" s="34" t="n">
-        <v>8</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="K25" s="34"/>
       <c r="L25" s="46" t="s">
         <v>38</v>
       </c>
@@ -2029,11 +2015,17 @@
       <c r="A26" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B26" s="40"/>
-      <c r="C26" s="41"/>
+      <c r="B26" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="41" t="s">
+        <v>51</v>
+      </c>
       <c r="D26" s="31"/>
       <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
+      <c r="F26" s="31" t="n">
+        <v>24</v>
+      </c>
       <c r="G26" s="32"/>
       <c r="H26" s="26" t="str">
         <f aca="false">IF(AND(B26="",OR(C26&lt;&gt;"",D26&lt;&gt;"",E26&lt;&gt;"",F26&lt;&gt;"",G26&lt;&gt;"")),"A lorry must be selected",IF(AND(C26="",OR(D26&lt;&gt;"",E26&lt;&gt;"",F26&lt;&gt;"",G26&lt;&gt;"")),"A town must be selected",""))</f>
@@ -2043,13 +2035,11 @@
         <v>6</v>
       </c>
       <c r="J26" s="46" t="s">
-        <v>54</v>
-      </c>
-      <c r="K26" s="34" t="n">
-        <v>10</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="K26" s="34"/>
       <c r="L26" s="46" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2062,10 +2052,10 @@
       <c r="C27" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="31"/>
-      <c r="E27" s="31" t="n">
-        <v>17</v>
-      </c>
+      <c r="D27" s="31" t="n">
+        <v>24</v>
+      </c>
+      <c r="E27" s="31"/>
       <c r="F27" s="31"/>
       <c r="G27" s="32"/>
       <c r="H27" s="26" t="str">
@@ -2076,13 +2066,11 @@
         <v>7</v>
       </c>
       <c r="J27" s="47" t="s">
-        <v>56</v>
-      </c>
-      <c r="K27" s="43" t="n">
-        <v>0</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="K27" s="43"/>
       <c r="L27" s="47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2093,29 +2081,35 @@
         <v>32</v>
       </c>
       <c r="C28" s="41" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="D28" s="31"/>
       <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="32" t="n">
-        <v>17</v>
-      </c>
+      <c r="F28" s="31" t="n">
+        <v>24</v>
+      </c>
+      <c r="G28" s="32"/>
       <c r="H28" s="26" t="str">
         <f aca="false">IF(AND(B28="",OR(C28&lt;&gt;"",D28&lt;&gt;"",E28&lt;&gt;"",F28&lt;&gt;"",G28&lt;&gt;"")),"A lorry must be selected",IF(AND(C28="",OR(D28&lt;&gt;"",E28&lt;&gt;"",F28&lt;&gt;"",G28&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
       </c>
       <c r="J28" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B29" s="40"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="31"/>
+      <c r="B29" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" s="31" t="n">
+        <v>24</v>
+      </c>
       <c r="E29" s="31"/>
       <c r="F29" s="31"/>
       <c r="G29" s="32"/>
@@ -2128,18 +2122,24 @@
       <c r="A30" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B30" s="40"/>
-      <c r="C30" s="41"/>
+      <c r="B30" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" s="41" t="s">
+        <v>33</v>
+      </c>
       <c r="D30" s="31"/>
       <c r="E30" s="31"/>
-      <c r="F30" s="31"/>
+      <c r="F30" s="31" t="n">
+        <v>24</v>
+      </c>
       <c r="G30" s="32"/>
       <c r="H30" s="26" t="str">
         <f aca="false">IF(AND(B30="",OR(C30&lt;&gt;"",D30&lt;&gt;"",E30&lt;&gt;"",F30&lt;&gt;"",G30&lt;&gt;"")),"A lorry must be selected",IF(AND(C30="",OR(D30&lt;&gt;"",E30&lt;&gt;"",F30&lt;&gt;"",G30&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
       </c>
       <c r="J30" s="48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K30" s="48"/>
       <c r="L30" s="48"/>
@@ -2148,16 +2148,10 @@
       <c r="A31" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B31" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="C31" s="41" t="s">
-        <v>22</v>
-      </c>
+      <c r="B31" s="40"/>
+      <c r="C31" s="41"/>
       <c r="D31" s="31"/>
-      <c r="E31" s="31" t="n">
-        <v>12</v>
-      </c>
+      <c r="E31" s="31"/>
       <c r="F31" s="31"/>
       <c r="G31" s="32"/>
       <c r="H31" s="26" t="str">
@@ -2170,19 +2164,17 @@
         <v>22</v>
       </c>
       <c r="B32" s="40" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C32" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31" t="n">
-        <v>24</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="D32" s="31" t="n">
+        <v>66</v>
+      </c>
+      <c r="E32" s="31"/>
       <c r="F32" s="31"/>
-      <c r="G32" s="32" t="n">
-        <v>12</v>
-      </c>
+      <c r="G32" s="32"/>
       <c r="H32" s="26" t="str">
         <f aca="false">IF(AND(B32="",OR(C32&lt;&gt;"",D32&lt;&gt;"",E32&lt;&gt;"",F32&lt;&gt;"",G32&lt;&gt;"")),"A lorry must be selected",IF(AND(C32="",OR(D32&lt;&gt;"",E32&lt;&gt;"",F32&lt;&gt;"",G32&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2191,13 +2183,13 @@
         <v>1</v>
       </c>
       <c r="J32" s="49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K32" s="28" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="L32" s="49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2205,17 +2197,17 @@
         <v>23</v>
       </c>
       <c r="B33" s="40" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C33" s="41" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D33" s="31"/>
       <c r="E33" s="31"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="32" t="n">
-        <v>24</v>
-      </c>
+      <c r="F33" s="31" t="n">
+        <v>33</v>
+      </c>
+      <c r="G33" s="32"/>
       <c r="H33" s="26" t="str">
         <f aca="false">IF(AND(B33="",OR(C33&lt;&gt;"",D33&lt;&gt;"",E33&lt;&gt;"",F33&lt;&gt;"",G33&lt;&gt;"")),"A lorry must be selected",IF(AND(C33="",OR(D33&lt;&gt;"",E33&lt;&gt;"",F33&lt;&gt;"",G33&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2224,22 +2216,28 @@
         <v>2</v>
       </c>
       <c r="J33" s="50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K33" s="34"/>
       <c r="L33" s="50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B34" s="40"/>
-      <c r="C34" s="41"/>
+      <c r="B34" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="C34" s="41" t="s">
+        <v>61</v>
+      </c>
       <c r="D34" s="31"/>
       <c r="E34" s="31"/>
-      <c r="F34" s="31"/>
+      <c r="F34" s="31" t="n">
+        <v>33</v>
+      </c>
       <c r="G34" s="32"/>
       <c r="H34" s="26" t="str">
         <f aca="false">IF(AND(B34="",OR(C34&lt;&gt;"",D34&lt;&gt;"",E34&lt;&gt;"",F34&lt;&gt;"",G34&lt;&gt;"")),"A lorry must be selected",IF(AND(C34="",OR(D34&lt;&gt;"",E34&lt;&gt;"",F34&lt;&gt;"",G34&lt;&gt;"")),"A town must be selected",""))</f>
@@ -2255,7 +2253,7 @@
         <v>15</v>
       </c>
       <c r="L34" s="51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2457,11 +2455,9 @@
       <c r="J44" s="57" t="s">
         <v>68</v>
       </c>
-      <c r="K44" s="34" t="n">
+      <c r="K44" s="34"/>
+      <c r="L44" s="57" t="s">
         <v>40</v>
-      </c>
-      <c r="L44" s="57" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2486,7 +2482,7 @@
       </c>
       <c r="K45" s="43"/>
       <c r="L45" s="58" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
